--- a/List_package_candidate.xlsx
+++ b/List_package_candidate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sql\ssis_toolkit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DFA63E-271A-48AF-914D-F2F7101AA380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51DDBCB-5A5A-4E7C-B9C1-3D9CA3C22CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{E0DADEBC-BAAA-4F56-B97B-62BF73D6A750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DADEBC-BAAA-4F56-B97B-62BF73D6A750}"/>
   </bookViews>
   <sheets>
     <sheet name="PackagesCandidate" sheetId="1" r:id="rId1"/>

--- a/List_package_candidate.xlsx
+++ b/List_package_candidate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sql\ssis_toolkit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51DDBCB-5A5A-4E7C-B9C1-3D9CA3C22CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEEE1F9-BC5D-445C-B85B-56E045188EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DADEBC-BAAA-4F56-B97B-62BF73D6A750}"/>
   </bookViews>
@@ -2117,7 +2117,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8BF679-729A-4C2A-9A82-5F216F431FD4}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:AO167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3387,7 +3386,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3509,7 +3508,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3631,7 +3630,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3875,7 +3874,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3997,7 +3996,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4119,7 +4118,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4241,7 +4240,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4363,7 +4362,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -4485,7 +4484,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -4607,7 +4606,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -4729,7 +4728,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -4851,7 +4850,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4973,7 +4972,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5095,7 +5094,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5217,7 +5216,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5339,7 +5338,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5461,7 +5460,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -5583,7 +5582,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -5705,7 +5704,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5827,7 +5826,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5949,7 +5948,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -6071,7 +6070,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -6193,7 +6192,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -6315,7 +6314,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="36" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -6437,7 +6436,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -6559,7 +6558,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -6681,7 +6680,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -6803,7 +6802,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -7047,7 +7046,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -7169,7 +7168,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -7291,7 +7290,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -7413,7 +7412,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -7535,7 +7534,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -7657,7 +7656,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -7779,7 +7778,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -7901,7 +7900,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -8023,7 +8022,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -8145,7 +8144,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="51" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -8267,7 +8266,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="52" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
@@ -8389,7 +8388,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
@@ -8511,7 +8510,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
@@ -8633,7 +8632,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
@@ -8755,7 +8754,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -8877,7 +8876,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
       </c>
@@ -8999,7 +8998,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="58" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>56</v>
       </c>
@@ -9121,7 +9120,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
@@ -9243,7 +9242,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
@@ -9365,7 +9364,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
@@ -9487,7 +9486,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
@@ -9609,7 +9608,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="63" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
@@ -9731,7 +9730,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
@@ -9853,7 +9852,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
@@ -9975,7 +9974,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="66" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
@@ -10097,7 +10096,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="67" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
@@ -10219,7 +10218,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
@@ -10341,7 +10340,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
@@ -10463,7 +10462,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
@@ -10585,7 +10584,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
@@ -10707,7 +10706,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="72" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
@@ -10829,7 +10828,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
@@ -10951,7 +10950,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
@@ -11073,7 +11072,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="75" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
@@ -11195,7 +11194,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="76" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
@@ -11317,7 +11316,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
@@ -11439,7 +11438,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
@@ -11561,7 +11560,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="79" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
@@ -11683,7 +11682,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
@@ -11805,7 +11804,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="81" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
@@ -11927,7 +11926,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
@@ -12049,7 +12048,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>81</v>
       </c>
@@ -12171,7 +12170,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>82</v>
       </c>
@@ -12293,7 +12292,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
@@ -12415,7 +12414,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>84</v>
       </c>
@@ -12537,7 +12536,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
@@ -12659,7 +12658,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="88" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>86</v>
       </c>
@@ -12781,7 +12780,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>87</v>
       </c>
@@ -13025,7 +13024,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>89</v>
       </c>
@@ -13147,7 +13146,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="92" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>90</v>
       </c>
@@ -13269,7 +13268,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="93" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>91</v>
       </c>
@@ -13513,7 +13512,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="95" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>93</v>
       </c>
@@ -13635,7 +13634,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="96" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>94</v>
       </c>
@@ -13757,7 +13756,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="97" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
@@ -13879,7 +13878,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="98" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96</v>
       </c>
@@ -14001,7 +14000,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="99" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>97</v>
       </c>
@@ -14123,7 +14122,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>98</v>
       </c>
@@ -14245,7 +14244,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="101" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>99</v>
       </c>
@@ -14367,7 +14366,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>100</v>
       </c>
@@ -14489,7 +14488,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="103" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>101</v>
       </c>
@@ -14611,7 +14610,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="104" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>102</v>
       </c>
@@ -14733,7 +14732,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="105" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>103</v>
       </c>
@@ -14855,7 +14854,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="106" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>104</v>
       </c>
@@ -14977,7 +14976,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="107" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>105</v>
       </c>
@@ -15221,7 +15220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="109" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>107</v>
       </c>
@@ -15343,7 +15342,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="110" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>108</v>
       </c>
@@ -15587,7 +15586,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>110</v>
       </c>
@@ -15709,7 +15708,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="113" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>111</v>
       </c>
@@ -15831,7 +15830,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="114" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>112</v>
       </c>
@@ -15953,7 +15952,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="115" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>113</v>
       </c>
@@ -16075,7 +16074,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="116" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>114</v>
       </c>
@@ -16197,7 +16196,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="117" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>115</v>
       </c>
@@ -16319,7 +16318,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="118" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>116</v>
       </c>
@@ -16441,7 +16440,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="119" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>117</v>
       </c>
@@ -16563,7 +16562,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="120" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>118</v>
       </c>
@@ -16685,7 +16684,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="121" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>119</v>
       </c>
@@ -16807,7 +16806,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="122" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>120</v>
       </c>
@@ -16929,7 +16928,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="123" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>121</v>
       </c>
@@ -17051,7 +17050,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="124" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>122</v>
       </c>
@@ -17173,7 +17172,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="125" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>123</v>
       </c>
@@ -17295,7 +17294,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="126" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>124</v>
       </c>
@@ -17417,7 +17416,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="127" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>125</v>
       </c>
@@ -17539,7 +17538,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="128" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>126</v>
       </c>
@@ -17661,7 +17660,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="129" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>127</v>
       </c>
@@ -17783,7 +17782,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="130" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>128</v>
       </c>
@@ -17905,7 +17904,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="131" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>129</v>
       </c>
@@ -18027,7 +18026,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>130</v>
       </c>
@@ -18149,7 +18148,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="133" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>131</v>
       </c>
@@ -18271,7 +18270,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="134" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>132</v>
       </c>
@@ -18393,7 +18392,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="135" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>133</v>
       </c>
@@ -18515,7 +18514,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="136" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>134</v>
       </c>
@@ -18637,7 +18636,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="137" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>135</v>
       </c>
@@ -18759,7 +18758,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="138" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>136</v>
       </c>
@@ -18881,7 +18880,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="139" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>137</v>
       </c>
@@ -19003,7 +19002,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="140" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>138</v>
       </c>
@@ -19125,7 +19124,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="141" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>139</v>
       </c>
@@ -19247,7 +19246,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="142" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>140</v>
       </c>
@@ -19369,7 +19368,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="143" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>141</v>
       </c>
@@ -19491,7 +19490,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="144" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>142</v>
       </c>
@@ -19613,7 +19612,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="145" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>143</v>
       </c>
@@ -19735,7 +19734,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="146" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>144</v>
       </c>
@@ -19857,7 +19856,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="147" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>145</v>
       </c>
@@ -19979,7 +19978,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="148" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>146</v>
       </c>
@@ -20101,7 +20100,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="149" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>147</v>
       </c>
@@ -20223,7 +20222,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="150" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>148</v>
       </c>
@@ -20345,7 +20344,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="151" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>149</v>
       </c>
@@ -20467,7 +20466,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="152" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>150</v>
       </c>
@@ -20589,7 +20588,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="153" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>151</v>
       </c>
@@ -20711,7 +20710,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="154" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>152</v>
       </c>
@@ -20833,7 +20832,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="155" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>153</v>
       </c>
@@ -20955,7 +20954,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="156" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>154</v>
       </c>
@@ -21077,7 +21076,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="157" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>155</v>
       </c>
@@ -21199,7 +21198,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="158" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>156</v>
       </c>
@@ -21321,7 +21320,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="159" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>157</v>
       </c>
@@ -21443,7 +21442,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="160" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>158</v>
       </c>
@@ -21565,7 +21564,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="161" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>159</v>
       </c>
@@ -21687,7 +21686,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="162" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>160</v>
       </c>
@@ -21809,7 +21808,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="163" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>161</v>
       </c>
@@ -21931,7 +21930,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="164" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>162</v>
       </c>
@@ -22053,7 +22052,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="165" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>163</v>
       </c>
@@ -22175,7 +22174,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>164</v>
       </c>
@@ -22297,7 +22296,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="167" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>165</v>
       </c>
@@ -22420,13 +22419,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AO167" xr:uid="{AE8BF679-729A-4C2A-9A82-5F216F431FD4}">
-    <filterColumn colId="39">
-      <filters>
-        <filter val="P1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
